--- a/UTCUTS/A1_Outputs/A-O_AR_Projections.xlsx
+++ b/UTCUTS/A1_Outputs/A-O_AR_Projections.xlsx
@@ -14798,7 +14798,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{132D913E-DE17-4F86-8CDF-ED7075762D9A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{704DD8CB-7C80-497A-B05F-1C5601799703}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
